--- a/eval/gold_scenarios/workpapers/q3_pass_dc9_02/billing_calc.xlsx
+++ b/eval/gold_scenarios/workpapers/q3_pass_dc9_02/billing_calc.xlsx
@@ -431,7 +431,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Epsilon Holdings</t>
+          <t>Eta Growth Mandate</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>272008148</v>
+        <v>426873051</v>
       </c>
     </row>
     <row r="5">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2040061</v>
+        <v>3201547</v>
       </c>
     </row>
     <row r="7">
@@ -487,7 +487,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SY</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-15</t>
         </is>
       </c>
     </row>
